--- a/Documentacion Sprint (01 - 11)/Sprint 5 documentacion/Sprint_05_Backlog_ICARO.xlsx
+++ b/Documentacion Sprint (01 - 11)/Sprint 5 documentacion/Sprint_05_Backlog_ICARO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentos Base\Sprint 5 documentacion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentacion Sprint (01 - 11)\Sprint 5 documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63FB691-85F0-462A-BFE0-59562516E7E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6A1220-6FBF-4656-9396-E60C319C039B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SPRINT BACKLOG" sheetId="4" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="221">
   <si>
     <t>ICARO CONSTRUCTORES BMGM S.A.S.</t>
   </si>
@@ -683,13 +683,16 @@
   </si>
   <si>
     <t>RESUMEN DE CASOS DE PRUEBA — SPRINT 05 (CP-69 a CP-086)</t>
+  </si>
+  <si>
+    <t>Los estados presentados en este documento corresponden al estado del Product/Sprint Backlog al cierre del Sprint respectivo. Debido a la naturaleza iterativa e incremental del proyecto, los elementos identificados como pendientes, diferidos o parcialmente implementados pudieron ser desarrollados y completados en sprints posteriores. Para conocer el estado definitivo de cada historia de usuario o historia técnica, debe consultarse el Product Backlog Consolidado al cierre del proyecto.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -779,8 +782,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -823,8 +833,13 @@
         <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -927,11 +942,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1011,6 +1042,9 @@
     <xf numFmtId="49" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1070,8 +1104,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Notas" xfId="1" builtinId="10"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1371,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3547449E-F765-40AD-8CC7-9ECB59135B7A}">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.5703125" customWidth="1"/>
@@ -1389,124 +1424,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
     </row>
     <row r="3" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="33"/>
       <c r="G3" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="H3" s="33" t="s">
+      <c r="H3" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="36"/>
     </row>
     <row r="4" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="36">
+      <c r="B4" s="37">
         <v>46123</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="33"/>
       <c r="G4" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="H4" s="36">
+      <c r="H4" s="37">
         <v>46157</v>
       </c>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="33"/>
     </row>
     <row r="5" spans="1:12" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="40"/>
       <c r="G5" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="H5" s="30" t="s">
+      <c r="H5" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="33"/>
     </row>
     <row r="6" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="40">
+      <c r="B6" s="41">
         <v>22</v>
       </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="36"/>
       <c r="G6" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="H6" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="33"/>
     </row>
     <row r="7" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
@@ -1775,13 +1810,13 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
       <c r="F14" s="7">
         <v>22</v>
       </c>
@@ -1794,19 +1829,71 @@
       <c r="K14" s="10"/>
       <c r="L14" s="10"/>
     </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="27"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="27"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="27"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="27"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="27"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="27"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="A14:E14"/>
+  <mergeCells count="12">
+    <mergeCell ref="A16:E22"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="H4:L4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1823,12 +1910,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -2033,14 +2120,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="46" t="s">
         <v>219</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
@@ -2441,11 +2528,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
